--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136935580</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136938392</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938413</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938612</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136939007</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136935580</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136938392</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938413</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938612</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136939007</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136938584</v>
       </c>
       <c r="B15" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137095107</v>
       </c>
       <c r="B16" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>136938896</v>
       </c>
       <c r="B17" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>136935151</v>
       </c>
       <c r="B3" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136938584</v>
       </c>
       <c r="B15" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137095107</v>
       </c>
       <c r="B16" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>136938896</v>
       </c>
       <c r="B17" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -2179,16 +2179,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnhöjden, Björnhöjden, Vstm</t>
@@ -2310,16 +2302,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lackalansåsen, Vstm</t>
@@ -2441,21 +2425,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnhöjden, Björnhöjden, Vstm</t>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>136935151</v>
       </c>
       <c r="B3" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136938584</v>
       </c>
       <c r="B15" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>137095107</v>
       </c>
       <c r="B16" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136938896</v>
       </c>
       <c r="B17" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136935660</v>
       </c>
       <c r="B18" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>137095402</v>
       </c>
       <c r="B19" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>137100755</v>
       </c>
       <c r="B20" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136938584</v>
       </c>
       <c r="B15" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>137095107</v>
       </c>
       <c r="B16" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136938896</v>
       </c>
       <c r="B17" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136938584</v>
       </c>
       <c r="B15" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>137095107</v>
       </c>
       <c r="B16" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136935936</v>
       </c>
       <c r="B4" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136935673</v>
       </c>
       <c r="B5" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136935690</v>
       </c>
       <c r="B6" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136935727</v>
       </c>
       <c r="B7" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136937288</v>
       </c>
       <c r="B8" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137095123</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136935580</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136938392</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136938413</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136938612</v>
       </c>
       <c r="B13" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136939007</v>
       </c>
       <c r="B14" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136938584</v>
       </c>
       <c r="B15" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>137095107</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136938896</v>
       </c>
       <c r="B17" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
